--- a/site/sk_leads.xlsx
+++ b/site/sk_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saskatchewan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Saskatchewan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/sk_leads.xlsx
+++ b/site/sk_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X267"/>
+  <dimension ref="A1:X258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19068,654 +19068,6 @@
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="n">
-        <v>258</v>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Echo Lake Cu Zone or ALF Cu Zone</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>0142</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver, Zinc</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Deposit: Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I259" t="b">
-        <v>0</v>
-      </c>
-      <c r="J259" t="b">
-        <v>0</v>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
-      <c r="O259" t="n">
-        <v>0</v>
-      </c>
-      <c r="P259" t="inlineStr"/>
-      <c r="Q259" t="inlineStr"/>
-      <c r="R259" t="inlineStr"/>
-      <c r="S259" t="n">
-        <v>8</v>
-      </c>
-      <c r="T259" t="n">
-        <v>200</v>
-      </c>
-      <c r="U259" t="n">
-        <v>24</v>
-      </c>
-      <c r="V259" t="n">
-        <v>54.64028</v>
-      </c>
-      <c r="W259" t="n">
-        <v>-102.00002</v>
-      </c>
-      <c r="X259" t="inlineStr">
-        <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0142</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
-        <v>259</v>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Alimak and Alimak Raise Zones</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>5118</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Deposit: Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I260" t="b">
-        <v>0</v>
-      </c>
-      <c r="J260" t="b">
-        <v>0</v>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="n">
-        <v>0</v>
-      </c>
-      <c r="P260" t="inlineStr"/>
-      <c r="Q260" t="inlineStr"/>
-      <c r="R260" t="inlineStr"/>
-      <c r="S260" t="n">
-        <v>8</v>
-      </c>
-      <c r="T260" t="n">
-        <v>200</v>
-      </c>
-      <c r="U260" t="n">
-        <v>24</v>
-      </c>
-      <c r="V260" t="n">
-        <v>56.00088</v>
-      </c>
-      <c r="W260" t="n">
-        <v>-104.28438</v>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5118</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>260</v>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Fox Lake Uranium Deposit</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>5539</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>Uranium, Arsenic, Cobalt, Copper, Lead, Nickel, Vanadium</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Deposit: Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I261" t="b">
-        <v>0</v>
-      </c>
-      <c r="J261" t="b">
-        <v>0</v>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="n">
-        <v>0</v>
-      </c>
-      <c r="P261" t="inlineStr"/>
-      <c r="Q261" t="inlineStr"/>
-      <c r="R261" t="inlineStr"/>
-      <c r="S261" t="n">
-        <v>1</v>
-      </c>
-      <c r="T261" t="n">
-        <v>25</v>
-      </c>
-      <c r="U261" t="n">
-        <v>24</v>
-      </c>
-      <c r="V261" t="n">
-        <v>57.75895</v>
-      </c>
-      <c r="W261" t="n">
-        <v>-105.23771</v>
-      </c>
-      <c r="X261" t="inlineStr">
-        <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5539</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>261</v>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>PAM Au Zone and North Tensional Vein Au Showing</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>2443a</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Deposit: Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I262" t="b">
-        <v>0</v>
-      </c>
-      <c r="J262" t="b">
-        <v>0</v>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
-      <c r="O262" t="n">
-        <v>0</v>
-      </c>
-      <c r="P262" t="inlineStr"/>
-      <c r="Q262" t="inlineStr"/>
-      <c r="R262" t="inlineStr"/>
-      <c r="S262" t="n">
-        <v>8</v>
-      </c>
-      <c r="T262" t="n">
-        <v>200</v>
-      </c>
-      <c r="U262" t="n">
-        <v>24</v>
-      </c>
-      <c r="V262" t="n">
-        <v>56.0039</v>
-      </c>
-      <c r="W262" t="n">
-        <v>-104.26668</v>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2443a</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
-        <v>262</v>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>BJ Uranium Deposit: BJ Main and BJ East Zones</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>2170</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>Uranium, Arsenic, Copper, Graphite, Nickel</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>Deposit: Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I263" t="b">
-        <v>0</v>
-      </c>
-      <c r="J263" t="b">
-        <v>0</v>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
-      <c r="O263" t="n">
-        <v>0</v>
-      </c>
-      <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="inlineStr"/>
-      <c r="R263" t="inlineStr"/>
-      <c r="S263" t="n">
-        <v>4</v>
-      </c>
-      <c r="T263" t="n">
-        <v>100</v>
-      </c>
-      <c r="U263" t="n">
-        <v>24</v>
-      </c>
-      <c r="V263" t="n">
-        <v>57.70085</v>
-      </c>
-      <c r="W263" t="n">
-        <v>-104.99446</v>
-      </c>
-      <c r="X263" t="inlineStr">
-        <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2170</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
-        <v>263</v>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Rod Main Gold Zone; Rod C Gold Zone (portion of the Jolu Mine)</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>1877a</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Iron, Molybdenum</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Deposit: Post-Production</t>
-        </is>
-      </c>
-      <c r="I264" t="b">
-        <v>0</v>
-      </c>
-      <c r="J264" t="b">
-        <v>0</v>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
-      <c r="O264" t="n">
-        <v>0</v>
-      </c>
-      <c r="P264" t="inlineStr"/>
-      <c r="Q264" t="inlineStr"/>
-      <c r="R264" t="inlineStr"/>
-      <c r="S264" t="n">
-        <v>8</v>
-      </c>
-      <c r="T264" t="n">
-        <v>200</v>
-      </c>
-      <c r="U264" t="n">
-        <v>19</v>
-      </c>
-      <c r="V264" t="n">
-        <v>56.00237</v>
-      </c>
-      <c r="W264" t="n">
-        <v>-104.27771</v>
-      </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1877a</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
-        <v>264</v>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Jolu Mine; Rod South Gold Zone</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>1877b</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Iron, Molybdenum</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Deposit: Post-Production</t>
-        </is>
-      </c>
-      <c r="I265" t="b">
-        <v>0</v>
-      </c>
-      <c r="J265" t="b">
-        <v>0</v>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
-      <c r="O265" t="n">
-        <v>0</v>
-      </c>
-      <c r="P265" t="inlineStr"/>
-      <c r="Q265" t="inlineStr"/>
-      <c r="R265" t="inlineStr"/>
-      <c r="S265" t="n">
-        <v>8</v>
-      </c>
-      <c r="T265" t="n">
-        <v>200</v>
-      </c>
-      <c r="U265" t="n">
-        <v>19</v>
-      </c>
-      <c r="V265" t="n">
-        <v>56.00278</v>
-      </c>
-      <c r="W265" t="n">
-        <v>-104.28057</v>
-      </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1877b</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
-        <v>265</v>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Martin Lake Mine</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>Uranium, Copper, Gold, Lead, Selenium</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Deposit: Post-Production [Institutional Control Program]</t>
-        </is>
-      </c>
-      <c r="I266" t="b">
-        <v>0</v>
-      </c>
-      <c r="J266" t="b">
-        <v>0</v>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
-      <c r="O266" t="n">
-        <v>0</v>
-      </c>
-      <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="inlineStr"/>
-      <c r="R266" t="inlineStr"/>
-      <c r="S266" t="n">
-        <v>2</v>
-      </c>
-      <c r="T266" t="n">
-        <v>50</v>
-      </c>
-      <c r="U266" t="n">
-        <v>19</v>
-      </c>
-      <c r="V266" t="n">
-        <v>59.55079</v>
-      </c>
-      <c r="W266" t="n">
-        <v>-108.54089</v>
-      </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1361</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="n">
-        <v>266</v>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Redberry Lake</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>5044</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>Magnesium Sulphate</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Deposit: Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I267" t="b">
-        <v>0</v>
-      </c>
-      <c r="J267" t="b">
-        <v>0</v>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
-      <c r="O267" t="n">
-        <v>0</v>
-      </c>
-      <c r="P267" t="inlineStr"/>
-      <c r="Q267" t="inlineStr"/>
-      <c r="R267" t="inlineStr"/>
-      <c r="S267" t="n">
-        <v>3</v>
-      </c>
-      <c r="T267" t="n">
-        <v>75</v>
-      </c>
-      <c r="U267" t="n">
-        <v>19</v>
-      </c>
-      <c r="V267" t="n">
-        <v>52.69009</v>
-      </c>
-      <c r="W267" t="n">
-        <v>-107.16763</v>
-      </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
